--- a/outputs/tables/ame_bootstrap_results_intersect.xlsx
+++ b/outputs/tables/ame_bootstrap_results_intersect.xlsx
@@ -458,25 +458,25 @@
         <v>0.0016090009769148</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00120831523175791</v>
+        <v>0.00113404844833201</v>
       </c>
       <c r="E2" t="n">
-        <v>1.33160696366789</v>
+        <v>1.41881149723486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.182989375449534</v>
+        <v>0.15595397985124</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.00025158356816211</v>
+        <v>-0.000360109859554306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00361404749444919</v>
+        <v>0.00371849295465895</v>
       </c>
       <c r="I2" t="n">
         <v>0.95</v>
       </c>
       <c r="J2" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -493,25 +493,25 @@
         <v>-0.00110721948172509</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000951733091223432</v>
+        <v>0.000880616175831688</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.16337184441258</v>
+        <v>-1.2573235787764</v>
       </c>
       <c r="F3" t="n">
-        <v>0.24467866788978</v>
+        <v>0.208636489308004</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00270929146387164</v>
+        <v>-0.00279232834272061</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000783711722953105</v>
+        <v>0.000680310645803894</v>
       </c>
       <c r="I3" t="n">
         <v>0.95</v>
       </c>
       <c r="J3" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -528,25 +528,25 @@
         <v>0.00326490334741035</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00121942591776166</v>
+        <v>0.00112403272664267</v>
       </c>
       <c r="E4" t="n">
-        <v>2.67741016477927</v>
+        <v>2.90463370863067</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00741937459464122</v>
+        <v>0.00367683118405742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00096891390717132</v>
+        <v>0.000860593246908393</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00580701464030184</v>
+        <v>0.00537339004960961</v>
       </c>
       <c r="I4" t="n">
         <v>0.95</v>
       </c>
       <c r="J4" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -563,25 +563,25 @@
         <v>-0.0064223040363046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0010177472572367</v>
+        <v>0.00101982653589168</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.31031328322309</v>
+        <v>-6.29744746805329</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00000000027847119187386</v>
+        <v>0.000000000302586855295568</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.00810866686348877</v>
+        <v>-0.00829657381827767</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00463579836617421</v>
+        <v>-0.00445889813321201</v>
       </c>
       <c r="I5" t="n">
         <v>0.95</v>
       </c>
       <c r="J5" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -598,25 +598,25 @@
         <v>-0.0104997933322489</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00136784115138134</v>
+        <v>0.00124103522167705</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.67617886159187</v>
+        <v>-8.46051195715479</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0000000000000163904233750311</v>
+        <v>0.0000000000000000266206251493488</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0128086068039925</v>
+        <v>-0.0131532568107853</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00793179262397158</v>
+        <v>-0.00814372067474264</v>
       </c>
       <c r="I6" t="n">
         <v>0.95</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -633,25 +633,25 @@
         <v>0.00752082052053715</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000947361316696493</v>
+        <v>0.000967659370219797</v>
       </c>
       <c r="E7" t="n">
-        <v>7.93870341546424</v>
+        <v>7.77217764018432</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00000000000000204305644757884</v>
+        <v>0.00000000000000771481507935927</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0063486682301857</v>
+        <v>0.00566012653836587</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00944839936796459</v>
+        <v>0.00949918274123358</v>
       </c>
       <c r="I7" t="n">
         <v>0.95</v>
       </c>
       <c r="J7" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -668,25 +668,25 @@
         <v>0.00226686297542257</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00154085763282066</v>
+        <v>0.00172902713345512</v>
       </c>
       <c r="E8" t="n">
-        <v>1.47116964418894</v>
+        <v>1.31106269621848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.141245244335647</v>
+        <v>0.189836582533632</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0000417467711398432</v>
+        <v>-0.00103176155102993</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00542677318122518</v>
+        <v>0.00533508558319503</v>
       </c>
       <c r="I8" t="n">
         <v>0.95</v>
       </c>
       <c r="J8" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -703,25 +703,25 @@
         <v>-0.00261693212117435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00129215698549785</v>
+        <v>0.00135524729879659</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.02524317907556</v>
+        <v>-1.93096280176917</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0428423998975276</v>
+        <v>0.0534876527339988</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00463798398295456</v>
+        <v>-0.0054239215667798</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.000143083731197794</v>
+        <v>-0.0000467584752322648</v>
       </c>
       <c r="I9" t="n">
         <v>0.95</v>
       </c>
       <c r="J9" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -738,25 +738,25 @@
         <v>0.00561336312330426</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00140667193628497</v>
+        <v>0.00170082297021929</v>
       </c>
       <c r="E10" t="n">
-        <v>3.99052755550751</v>
+        <v>3.30038059315517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0000659264887168859</v>
+        <v>0.00096553791196266</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00352245582055798</v>
+        <v>0.00230540526430006</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00879894987643577</v>
+        <v>0.00860293197140209</v>
       </c>
       <c r="I10" t="n">
         <v>0.95</v>
       </c>
       <c r="J10" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -773,25 +773,25 @@
         <v>-0.0145457357380013</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00234850275940892</v>
+        <v>0.00234319276801653</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.19362088450868</v>
+        <v>-6.20765646623004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00000000058797554968387</v>
+        <v>0.000000000537805536105085</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0191974866207221</v>
+        <v>-0.0193019310870183</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0108974399979106</v>
+        <v>-0.0104493228765197</v>
       </c>
       <c r="I11" t="n">
         <v>0.95</v>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -808,25 +808,25 @@
         <v>-0.0168599998533428</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00222684388078582</v>
+        <v>0.0024636646130934</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.57125364683992</v>
+        <v>-6.84346390484264</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0000000000000369639510147196</v>
+        <v>0.00000000000773008087430971</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0208019418678916</v>
+        <v>-0.0223302165252373</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0127042903324415</v>
+        <v>-0.0131228255690031</v>
       </c>
       <c r="I12" t="n">
         <v>0.95</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -843,25 +843,25 @@
         <v>0.0102421083283208</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00173288150783374</v>
+        <v>0.00157607039838512</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9104493192523</v>
+        <v>6.49850941862441</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00000000341175812414624</v>
+        <v>0.0000000000811197174865278</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00744379705171873</v>
+        <v>0.00743775479193596</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0140072570716966</v>
+        <v>0.0133151004060009</v>
       </c>
       <c r="I13" t="n">
         <v>0.95</v>
       </c>
       <c r="J13" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -878,25 +878,25 @@
         <v>0.000665841493206454</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00338691752104734</v>
+        <v>0.00284674643654628</v>
       </c>
       <c r="E14" t="n">
-        <v>0.196592178306295</v>
+        <v>0.233895609618911</v>
       </c>
       <c r="F14" t="n">
-        <v>0.844146691973525</v>
+        <v>0.815066021705083</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00531327527309714</v>
+        <v>-0.0046894374472427</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00640782222785221</v>
+        <v>0.006536027123258</v>
       </c>
       <c r="I14" t="n">
         <v>0.95</v>
       </c>
       <c r="J14" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -913,25 +913,25 @@
         <v>0.00164247907226672</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00277292302310515</v>
+        <v>0.00258925053405563</v>
       </c>
       <c r="E15" t="n">
-        <v>0.592327684029053</v>
+        <v>0.634345363904992</v>
       </c>
       <c r="F15" t="n">
-        <v>0.553631181174309</v>
+        <v>0.52585545745178</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.00239354871984253</v>
+        <v>-0.00272475959876373</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00804486414438871</v>
+        <v>0.00719062139827993</v>
       </c>
       <c r="I15" t="n">
         <v>0.95</v>
       </c>
       <c r="J15" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -948,25 +948,25 @@
         <v>0.00789901933451888</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00346989951702538</v>
+        <v>0.00347366055131838</v>
       </c>
       <c r="E16" t="n">
-        <v>2.27644036830508</v>
+        <v>2.27397559946407</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0228196658670791</v>
+        <v>0.0229674536469925</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00180202200671553</v>
+        <v>0.000915369271817094</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0145582132658608</v>
+        <v>0.0140196835620843</v>
       </c>
       <c r="I16" t="n">
         <v>0.95</v>
       </c>
       <c r="J16" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -983,25 +983,25 @@
         <v>-0.0274319468949868</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00330873623107976</v>
+        <v>0.00318634904714336</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.29076268978829</v>
+        <v>-8.60920962804757</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000000000000000112524587657501</v>
+        <v>0.00000000000000000735660154662745</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0319536003773869</v>
+        <v>-0.0337825685444756</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0213219450266867</v>
+        <v>-0.0213455447530551</v>
       </c>
       <c r="I17" t="n">
         <v>0.95</v>
       </c>
       <c r="J17" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1018,25 +1018,25 @@
         <v>-0.0328954399042909</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00384799242717892</v>
+        <v>0.00374369623588279</v>
       </c>
       <c r="E18" t="n">
-        <v>-8.54872781763959</v>
+        <v>-8.78688809978567</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0000000000000000124452614986214</v>
+        <v>0.00000000000000000153759801657382</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0396017666929785</v>
+        <v>-0.0397571293830363</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0263269381958003</v>
+        <v>-0.0262708242061547</v>
       </c>
       <c r="I18" t="n">
         <v>0.95</v>
       </c>
       <c r="J18" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1053,25 +1053,25 @@
         <v>0.0229987346417775</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0026025996574611</v>
+        <v>0.00269900236680277</v>
       </c>
       <c r="E19" t="n">
-        <v>8.83683150262664</v>
+        <v>8.5211983971032</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000000000000000000984714849737053</v>
+        <v>0.0000000000000000157910764843732</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0187318598799987</v>
+        <v>0.0183098417088366</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0273078025995576</v>
+        <v>0.0285341948554532</v>
       </c>
       <c r="I19" t="n">
         <v>0.95</v>
       </c>
       <c r="J19" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1088,25 +1088,25 @@
         <v>0.00484924676073153</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00501915140148151</v>
+        <v>0.00535183639730458</v>
       </c>
       <c r="E20" t="n">
-        <v>0.966148731695994</v>
+        <v>0.906090246550478</v>
       </c>
       <c r="F20" t="n">
-        <v>0.33396976266733</v>
+        <v>0.36488808734544</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.00505596873434817</v>
+        <v>-0.00605955014156218</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0122223606190642</v>
+        <v>0.0151315284814468</v>
       </c>
       <c r="I20" t="n">
         <v>0.95</v>
       </c>
       <c r="J20" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1123,25 +1123,25 @@
         <v>-0.00106949567113231</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00360523228844003</v>
+        <v>0.00356514401045866</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.296650974352357</v>
+        <v>-0.299986667577761</v>
       </c>
       <c r="F21" t="n">
-        <v>0.766732989715045</v>
+        <v>0.764187325289217</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.00641488950244355</v>
+        <v>-0.00758243010212979</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00560266925801486</v>
+        <v>0.00699371266839249</v>
       </c>
       <c r="I21" t="n">
         <v>0.95</v>
       </c>
       <c r="J21" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1158,25 +1158,25 @@
         <v>0.0165165726156818</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00509435767258548</v>
+        <v>0.0050202251576618</v>
       </c>
       <c r="E22" t="n">
-        <v>3.242130544654</v>
+        <v>3.2900063437343</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00118639663941117</v>
+        <v>0.00100185124064887</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00807405245405871</v>
+        <v>0.00750889190338349</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0260598019355188</v>
+        <v>0.0258509450024813</v>
       </c>
       <c r="I22" t="n">
         <v>0.95</v>
       </c>
       <c r="J22" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1193,25 +1193,25 @@
         <v>-0.0479195179557246</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00465169516853773</v>
+        <v>0.00465230115554023</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.3015172360893</v>
+        <v>-10.300175408606</v>
       </c>
       <c r="F23" t="n">
-        <v>0.000000000000000000000000693586121494932</v>
+        <v>0.000000000000000000000000703329362014049</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0578228916944436</v>
+        <v>-0.0575761314147718</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0402049486303345</v>
+        <v>-0.0388737424010292</v>
       </c>
       <c r="I23" t="n">
         <v>0.95</v>
       </c>
       <c r="J23" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1228,25 +1228,25 @@
         <v>-0.0599893730627924</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00571645953538202</v>
+        <v>0.00543057833062747</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.4941481158903</v>
+        <v>-11.0465901439011</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0000000000000000000000000919029455912165</v>
+        <v>0.000000000000000000000000000227700077577467</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0693548599947692</v>
+        <v>-0.0701223173068153</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0483284623947198</v>
+        <v>-0.0477687558697703</v>
       </c>
       <c r="I24" t="n">
         <v>0.95</v>
       </c>
       <c r="J24" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1263,25 +1263,25 @@
         <v>0.0404189513607396</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00366409505934222</v>
+        <v>0.00420440323613982</v>
       </c>
       <c r="E25" t="n">
-        <v>11.0310869958695</v>
+        <v>9.61348117452439</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000000000000000000000000000270574729063647</v>
+        <v>0.000000000000000000000701367654210028</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0335840320566336</v>
+        <v>0.0323330150957612</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0473570899371713</v>
+        <v>0.0484019916488266</v>
       </c>
       <c r="I25" t="n">
         <v>0.95</v>
       </c>
       <c r="J25" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1298,25 +1298,25 @@
         <v>0.00777378169479977</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00482541239542473</v>
+        <v>0.00452765889013856</v>
       </c>
       <c r="E26" t="n">
-        <v>1.61100877143072</v>
+        <v>1.7169539233027</v>
       </c>
       <c r="F26" t="n">
-        <v>0.107177810653702</v>
+        <v>0.0859875911573656</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000674365875123097</v>
+        <v>0.000452802754558117</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0186792601605018</v>
+        <v>0.0186230967995637</v>
       </c>
       <c r="I26" t="n">
         <v>0.95</v>
       </c>
       <c r="J26" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1333,25 +1333,25 @@
         <v>-0.00508976866268246</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00187680835656857</v>
+        <v>0.00238568081044074</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.71192774950569</v>
+        <v>-2.13346590223113</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00668931714866553</v>
+        <v>0.0328865259113683</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.00897453935204807</v>
+        <v>-0.0103445422537713</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.00204543411314216</v>
+        <v>-0.00148007834707975</v>
       </c>
       <c r="I27" t="n">
         <v>0.95</v>
       </c>
       <c r="J27" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1368,25 +1368,25 @@
         <v>0.0158037784982477</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00408445008924269</v>
+        <v>0.00390651068367742</v>
       </c>
       <c r="E28" t="n">
-        <v>3.86925489428076</v>
+        <v>4.04549731920117</v>
       </c>
       <c r="F28" t="n">
-        <v>0.00010916846636778</v>
+        <v>0.0000522121632308173</v>
       </c>
       <c r="G28" t="n">
-        <v>0.00964123297582664</v>
+        <v>0.0100347399449955</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0238544982692121</v>
+        <v>0.024701313763339</v>
       </c>
       <c r="I28" t="n">
         <v>0.95</v>
       </c>
       <c r="J28" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1403,25 +1403,25 @@
         <v>-0.0246331848714063</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00386956880750163</v>
+        <v>0.0040965024371524</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.36587333029249</v>
+        <v>-6.01322353625392</v>
       </c>
       <c r="F29" t="n">
-        <v>0.000000000194181640911754</v>
+        <v>0.00000000181869973268905</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0325399087038228</v>
+        <v>-0.0342387109250449</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0186681849130782</v>
+        <v>-0.0191231271242263</v>
       </c>
       <c r="I29" t="n">
         <v>0.95</v>
       </c>
       <c r="J29" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1438,25 +1438,25 @@
         <v>-0.0281841018820941</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00540227524450729</v>
+        <v>0.00525276086413014</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.21707995362695</v>
+        <v>-5.3655787139591</v>
       </c>
       <c r="F30" t="n">
-        <v>0.000000181765813593284</v>
+        <v>0.000000080690080697159</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0405875413327419</v>
+        <v>-0.0411165222623113</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0231084500329453</v>
+        <v>-0.0216805485304317</v>
       </c>
       <c r="I30" t="n">
         <v>0.95</v>
       </c>
       <c r="J30" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1473,25 +1473,25 @@
         <v>0.0217679227931782</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00450425004742355</v>
+        <v>0.00425931745369998</v>
       </c>
       <c r="E31" t="n">
-        <v>4.83275185968628</v>
+        <v>5.11065987210436</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00000134658589033457</v>
+        <v>0.000000321035508191794</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0170652637764219</v>
+        <v>0.0165683753155402</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0331467732824043</v>
+        <v>0.0327432109747425</v>
       </c>
       <c r="I31" t="n">
         <v>0.95</v>
       </c>
       <c r="J31" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1508,25 +1508,25 @@
         <v>0.00505955320005135</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00539619144174696</v>
+        <v>0.00448233886280215</v>
       </c>
       <c r="E32" t="n">
-        <v>0.937615585857231</v>
+        <v>1.12877525660529</v>
       </c>
       <c r="F32" t="n">
-        <v>0.348441998765069</v>
+        <v>0.258992653102533</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.00329161744128905</v>
+        <v>-0.00324712696440496</v>
       </c>
       <c r="H32" t="n">
-        <v>0.015856514314957</v>
+        <v>0.0137378195526654</v>
       </c>
       <c r="I32" t="n">
         <v>0.95</v>
       </c>
       <c r="J32" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1543,25 +1543,25 @@
         <v>-0.00159540267069711</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00376762138786714</v>
+        <v>0.00359899297700744</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.423450900834883</v>
+        <v>-0.443291409816446</v>
       </c>
       <c r="F33" t="n">
-        <v>0.671966314208571</v>
+        <v>0.657554968357515</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.00859570474120416</v>
+        <v>-0.00848376084612323</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00479424318594789</v>
+        <v>0.00548696096218521</v>
       </c>
       <c r="I33" t="n">
         <v>0.95</v>
       </c>
       <c r="J33" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1578,25 +1578,25 @@
         <v>0.0139726022223693</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00488524413839697</v>
+        <v>0.00433993544440274</v>
       </c>
       <c r="E34" t="n">
-        <v>2.86016457448823</v>
+        <v>3.2195414888924</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00423421210556242</v>
+        <v>0.00128395779597719</v>
       </c>
       <c r="G34" t="n">
-        <v>0.00628743697937745</v>
+        <v>0.0062048448657305</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0227844304289206</v>
+        <v>0.0225052638352739</v>
       </c>
       <c r="I34" t="n">
         <v>0.95</v>
       </c>
       <c r="J34" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         <v>-0.0350964444542625</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00520721679238428</v>
+        <v>0.00504933835619694</v>
       </c>
       <c r="E35" t="n">
-        <v>-6.73996222043072</v>
+        <v>-6.95070165206683</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0000000000158427819771212</v>
+        <v>0.00000000000363473834551272</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0446116664687764</v>
+        <v>-0.0443902852722831</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.0260667432854287</v>
+        <v>-0.0256867628147364</v>
       </c>
       <c r="I35" t="n">
         <v>0.95</v>
       </c>
       <c r="J35" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1648,25 +1648,25 @@
         <v>-0.0420705671196537</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00565583087503771</v>
+        <v>0.00558699592028413</v>
       </c>
       <c r="E36" t="n">
-        <v>-7.43844150385299</v>
+        <v>-7.53008731703425</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000000000000101880070476811</v>
+        <v>0.0000000000000507064031385648</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0499991882662202</v>
+        <v>-0.0530244010057736</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0307715528996223</v>
+        <v>-0.0316864099894936</v>
       </c>
       <c r="I36" t="n">
         <v>0.95</v>
       </c>
       <c r="J36" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1683,25 +1683,25 @@
         <v>0.034441767795202</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00366400019978245</v>
+        <v>0.00352019373439274</v>
       </c>
       <c r="E37" t="n">
-        <v>9.40004528308894</v>
+        <v>9.78405462707963</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00000000000000000000545395938394567</v>
+        <v>0.000000000000000000000131821382507807</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0266473038118347</v>
+        <v>0.0269815638845894</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0403160698606925</v>
+        <v>0.0404445603441159</v>
       </c>
       <c r="I37" t="n">
         <v>0.95</v>
       </c>
       <c r="J37" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1718,25 +1718,25 @@
         <v>0.0131611237005886</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00832848080244194</v>
+        <v>0.00799188967544223</v>
       </c>
       <c r="E38" t="n">
-        <v>1.58025503243397</v>
+        <v>1.64680998300447</v>
       </c>
       <c r="F38" t="n">
-        <v>0.114048473365897</v>
+        <v>0.0995971087719519</v>
       </c>
       <c r="G38" t="n">
-        <v>0.000962938692326008</v>
+        <v>-0.000996980444340686</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0269660609895742</v>
+        <v>0.027919077801153</v>
       </c>
       <c r="I38" t="n">
         <v>0.95</v>
       </c>
       <c r="J38" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1753,25 +1753,25 @@
         <v>-0.00568828182180666</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00505766475670668</v>
+        <v>0.00515011830624512</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.12468542211378</v>
+        <v>-1.10449536953529</v>
       </c>
       <c r="F39" t="n">
-        <v>0.260722361276982</v>
+        <v>0.269378311088879</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0155410442838946</v>
+        <v>-0.0156924693589993</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00383375788226184</v>
+        <v>0.0046162260251453</v>
       </c>
       <c r="I39" t="n">
         <v>0.95</v>
       </c>
       <c r="J39" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1788,25 +1788,25 @@
         <v>0.0291876837094225</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00678614237316345</v>
+        <v>0.00678200657978718</v>
       </c>
       <c r="E40" t="n">
-        <v>4.30107152258527</v>
+        <v>4.30369439575778</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0000169974182503619</v>
+        <v>0.0000167973327036696</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0157578844647759</v>
+        <v>0.0159514648103398</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0405116791512639</v>
+        <v>0.041728828559815</v>
       </c>
       <c r="I40" t="n">
         <v>0.95</v>
       </c>
       <c r="J40" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1823,25 +1823,25 @@
         <v>-0.0590506596433476</v>
       </c>
       <c r="D41" t="n">
-        <v>0.006100875709985</v>
+        <v>0.00647760658585354</v>
       </c>
       <c r="E41" t="n">
-        <v>-9.67904649273584</v>
+        <v>-9.1161231946856</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000000000000000000000370151982107481</v>
+        <v>0.0000000000000000000778597349351031</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0723680259036268</v>
+        <v>-0.0732575425648209</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0462505140189564</v>
+        <v>-0.0479304333576659</v>
       </c>
       <c r="I41" t="n">
         <v>0.95</v>
       </c>
       <c r="J41" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -1858,25 +1858,25 @@
         <v>-0.0711540674489179</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00795888030995418</v>
+        <v>0.00844777777935568</v>
       </c>
       <c r="E42" t="n">
-        <v>-8.94021076808071</v>
+        <v>-8.42281476944163</v>
       </c>
       <c r="F42" t="n">
-        <v>0.000000000000000000388428810537893</v>
+        <v>0.0000000000000000367545320474777</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0860293534467617</v>
+        <v>-0.0876291821142018</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.0569176675801387</v>
+        <v>-0.0562365741806092</v>
       </c>
       <c r="I42" t="n">
         <v>0.95</v>
       </c>
       <c r="J42" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -1893,25 +1893,25 @@
         <v>0.0556057166613084</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00580749775117711</v>
+        <v>0.00663955925389354</v>
       </c>
       <c r="E43" t="n">
-        <v>9.57481501392538</v>
+        <v>8.37491082389247</v>
       </c>
       <c r="F43" t="n">
-        <v>0.00000000000000000000102039809612325</v>
+        <v>0.0000000000000000552657037117293</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0447468285468506</v>
+        <v>0.0442662087892926</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0649532369744399</v>
+        <v>0.0688742610121366</v>
       </c>
       <c r="I43" t="n">
         <v>0.95</v>
       </c>
       <c r="J43" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
